--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA87A18-0A48-42B6-B049-850347853C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB08D06-0D01-4D13-B4C1-D217C4327628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1138,6 +1138,12 @@
       <c r="AB3" t="s">
         <v>56</v>
       </c>
+      <c r="AC3">
+        <v>-23.862863999999998</v>
+      </c>
+      <c r="AD3">
+        <v>-64.173242000000002</v>
+      </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -1294,6 +1300,12 @@
       </c>
       <c r="AB5" t="s">
         <v>56</v>
+      </c>
+      <c r="AC5">
+        <v>-23.959973000000002</v>
+      </c>
+      <c r="AD5">
+        <v>-64.221204999999998</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB08D06-0D01-4D13-B4C1-D217C4327628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF12F990-5A6A-46A1-B572-69D18928820D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -230,24 +230,15 @@
     <t>PATChaco - Zona 5 -San Manuel - Riv B-S - Salta.xlsx</t>
   </si>
   <si>
-    <t>SAN MANUEL</t>
-  </si>
-  <si>
     <t>LA UNION - RIVADAVIA BANDA SUR - RIVADAVIA - SALTA</t>
   </si>
   <si>
-    <t>JESUS CARABAJAL</t>
-  </si>
-  <si>
     <t>BOVINOS: 120 - CAPRINOS: 200 - PORCINOS: 50</t>
   </si>
   <si>
     <t>no</t>
   </si>
   <si>
-    <t>ROSSETTO ASTORGA CRISTINA BEATRIZ</t>
-  </si>
-  <si>
     <t>rosetto.cristina@inta.gob.ar</t>
   </si>
   <si>
@@ -438,6 +429,15 @@
   </si>
   <si>
     <t>-22.05</t>
+  </si>
+  <si>
+    <t>Cristina B. Rossetto Astorga</t>
+  </si>
+  <si>
+    <t>San Manuel</t>
+  </si>
+  <si>
+    <t>Jesús Carabajal</t>
   </si>
 </sst>
 </file>
@@ -871,7 +871,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>26</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
@@ -978,10 +978,10 @@
         <v>29</v>
       </c>
       <c r="F2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" t="s">
         <v>110</v>
-      </c>
-      <c r="G2" t="s">
-        <v>113</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
@@ -1159,10 +1159,10 @@
         <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
         <v>45</v>
@@ -1316,28 +1316,28 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" t="s">
         <v>68</v>
       </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" t="s">
         <v>110</v>
-      </c>
-      <c r="G6" t="s">
-        <v>113</v>
       </c>
       <c r="H6" t="s">
         <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K6">
         <v>120</v>
@@ -1364,13 +1364,13 @@
         <v>48</v>
       </c>
       <c r="S6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T6" t="s">
         <v>49</v>
       </c>
       <c r="U6" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="V6" t="s">
         <v>36</v>
@@ -1379,7 +1379,7 @@
         <v>3878641984</v>
       </c>
       <c r="X6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
@@ -1387,10 +1387,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -1399,19 +1399,19 @@
         <v>29</v>
       </c>
       <c r="F7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" t="s">
         <v>110</v>
-      </c>
-      <c r="G7" t="s">
-        <v>113</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K7">
         <v>50</v>
@@ -1479,10 +1479,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -1491,19 +1491,19 @@
         <v>29</v>
       </c>
       <c r="F8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" t="s">
         <v>110</v>
-      </c>
-      <c r="G8" t="s">
-        <v>113</v>
       </c>
       <c r="H8" t="s">
         <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K8">
         <v>60</v>
@@ -1571,10 +1571,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -1583,19 +1583,19 @@
         <v>29</v>
       </c>
       <c r="F9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" t="s">
         <v>110</v>
-      </c>
-      <c r="G9" t="s">
-        <v>113</v>
       </c>
       <c r="H9" t="s">
         <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K9">
         <v>50</v>
@@ -1663,10 +1663,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1675,19 +1675,19 @@
         <v>29</v>
       </c>
       <c r="F10" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" t="s">
         <v>110</v>
-      </c>
-      <c r="G10" t="s">
-        <v>113</v>
       </c>
       <c r="H10" t="s">
         <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K10">
         <v>80</v>
@@ -1755,10 +1755,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1767,19 +1767,19 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" t="s">
         <v>110</v>
-      </c>
-      <c r="G11" t="s">
-        <v>113</v>
       </c>
       <c r="H11" t="s">
         <v>30</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K11">
         <v>60</v>
@@ -1847,10 +1847,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
@@ -1859,19 +1859,19 @@
         <v>29</v>
       </c>
       <c r="F12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" t="s">
         <v>110</v>
-      </c>
-      <c r="G12" t="s">
-        <v>113</v>
       </c>
       <c r="H12" t="s">
         <v>30</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K12">
         <v>40</v>
@@ -1939,10 +1939,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
@@ -1951,19 +1951,19 @@
         <v>29</v>
       </c>
       <c r="F13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" t="s">
         <v>110</v>
-      </c>
-      <c r="G13" t="s">
-        <v>113</v>
       </c>
       <c r="H13" t="s">
         <v>30</v>
       </c>
       <c r="I13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K13">
         <v>53</v>
@@ -2031,10 +2031,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
@@ -2043,19 +2043,19 @@
         <v>29</v>
       </c>
       <c r="F14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" t="s">
         <v>110</v>
-      </c>
-      <c r="G14" t="s">
-        <v>113</v>
       </c>
       <c r="H14" t="s">
         <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K14">
         <v>70</v>
@@ -2123,10 +2123,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
@@ -2135,19 +2135,19 @@
         <v>29</v>
       </c>
       <c r="F15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" t="s">
         <v>110</v>
-      </c>
-      <c r="G15" t="s">
-        <v>113</v>
       </c>
       <c r="H15" t="s">
         <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K15">
         <v>158</v>
@@ -2223,31 +2223,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -2261,11 +2261,11 @@
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -2279,11 +2279,11 @@
     </row>
     <row r="4" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D4" s="3">
         <v>7</v>
@@ -2297,11 +2297,11 @@
     </row>
     <row r="5" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D5" s="3">
         <v>8</v>
@@ -2315,11 +2315,11 @@
     </row>
     <row r="6" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3">
         <v>9</v>
@@ -2333,11 +2333,11 @@
     </row>
     <row r="7" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
@@ -2351,11 +2351,11 @@
     </row>
     <row r="8" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" s="3">
         <v>11</v>
@@ -2369,11 +2369,11 @@
     </row>
     <row r="9" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D9" s="3">
         <v>12</v>
@@ -2387,11 +2387,11 @@
     </row>
     <row r="10" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D10" s="3">
         <v>13</v>
@@ -2405,17 +2405,17 @@
     </row>
     <row r="11" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D11" s="3">
         <v>14</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F11" s="4">
         <v>-630652</v>

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF12F990-5A6A-46A1-B572-69D18928820D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00D740D-B158-4438-9ECC-E7F81A5980C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1381,6 +1381,12 @@
       <c r="X6" t="s">
         <v>71</v>
       </c>
+      <c r="AC6">
+        <v>-23.879200999999998</v>
+      </c>
+      <c r="AD6">
+        <v>-63.098135999999997</v>
+      </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7">

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00D740D-B158-4438-9ECC-E7F81A5980C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A484AC18-248A-4CDA-9A07-8417FEC5E31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1215,6 +1215,12 @@
       <c r="X4" t="s">
         <v>63</v>
       </c>
+      <c r="AC4">
+        <v>-24.23730001237</v>
+      </c>
+      <c r="AD4">
+        <v>-65.400272000000001</v>
+      </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5">

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A484AC18-248A-4CDA-9A07-8417FEC5E31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49018934-BDD4-4D0C-93BC-FA66DD187F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="217">
   <si>
     <t>archivo_origen</t>
   </si>
@@ -438,6 +438,243 @@
   </si>
   <si>
     <t>Jesús Carabajal</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento (formulario) Casa de Arco, Guachipas.xlsx</t>
+  </si>
+  <si>
+    <t>San Pedro, Abra Las Juntas</t>
+  </si>
+  <si>
+    <t>Casa de Arco, Las Juntas</t>
+  </si>
+  <si>
+    <t>Ariel Francisco Ontiveros</t>
+  </si>
+  <si>
+    <t>Vacuno: 340</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rios Silvia Fernanda </t>
+  </si>
+  <si>
+    <t>rios.fernanda@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Saldaño Rafael Bernardino</t>
+  </si>
+  <si>
+    <t>saldano.rafael@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento (formulario) LAS CEIBAS Alejo Alvarez.xlsx</t>
+  </si>
+  <si>
+    <t>Finca Las Ceibas</t>
+  </si>
+  <si>
+    <t>Las Ceibas / El Carril / Rosario de Lerma / Salta</t>
+  </si>
+  <si>
+    <t>Las Ceibas</t>
+  </si>
+  <si>
+    <t>Alejo Alvarez</t>
+  </si>
+  <si>
+    <t>Vacuno: 390</t>
+  </si>
+  <si>
+    <t>Bruno Luis Baldi</t>
+  </si>
+  <si>
+    <t>baldi.bruno@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Analía Gopar</t>
+  </si>
+  <si>
+    <t>INTA AER VALLE DE LERMA</t>
+  </si>
+  <si>
+    <t>gopar.analia@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento (formulario) San Pedro de Aranda.xlsx</t>
+  </si>
+  <si>
+    <t>San Pedro de Aranda</t>
+  </si>
+  <si>
+    <t>La Candelaria</t>
+  </si>
+  <si>
+    <t>Julio Batelino</t>
+  </si>
+  <si>
+    <t>vacunos: 430</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Federico Sebastian Vera</t>
+  </si>
+  <si>
+    <t>vera.federico@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Juan Orlando Colque</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>paoloacolque1980@gmail.com</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento (formulario)LA CIENEGA.xlsx</t>
+  </si>
+  <si>
+    <t>La Cienega</t>
+  </si>
+  <si>
+    <t>Balboa, Rosario de la Frontera</t>
+  </si>
+  <si>
+    <t>Benjamin Gomez; Ciro Gomez; Nanci Gomez; Diego Gomez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacuno: 110  Equinos; 12 </t>
+  </si>
+  <si>
+    <t>independiente</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento Finca Montecristo (Los Rosales).xlsx</t>
+  </si>
+  <si>
+    <t>Finca Montecristo</t>
+  </si>
+  <si>
+    <t>El Galpón (Los Rosales)</t>
+  </si>
+  <si>
+    <t>Familia Corbalan</t>
+  </si>
+  <si>
+    <t>Caprinos: 30 - Ovinos: 25</t>
+  </si>
+  <si>
+    <t>Eduardo Daniel Arias</t>
+  </si>
+  <si>
+    <t>arias.eduardo@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Hector Diaz</t>
+  </si>
+  <si>
+    <t>Diaz.Hector@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento Fraile Pintado.xlsx</t>
+  </si>
+  <si>
+    <t>Fraile Pintado</t>
+  </si>
+  <si>
+    <t>Joaquin V. Gonzalez (salta Forestal)</t>
+  </si>
+  <si>
+    <t>Albero Palma titular (tres familias en total)</t>
+  </si>
+  <si>
+    <t>Bovinos: 40</t>
+  </si>
+  <si>
+    <t>Lionel Rodriguez</t>
+  </si>
+  <si>
+    <t>rodriguez.lionel@Inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Carlos Gustavo Cabrera</t>
+  </si>
+  <si>
+    <t>cabrera.carlos@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento La Caldera.xlsx</t>
+  </si>
+  <si>
+    <t>Pequeños productores de la serrania de La Caldera</t>
+  </si>
+  <si>
+    <t>La Caldera</t>
+  </si>
+  <si>
+    <t>Pequeños productores de La Caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1800 cabezas bovina, Caprinos 1000  Ovinos 500 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">no </t>
+  </si>
+  <si>
+    <t>Jose C. Maidana</t>
+  </si>
+  <si>
+    <t>Municipalidad de La Caldera (Asuntos Rurales)</t>
+  </si>
+  <si>
+    <t>gauchomaidana09@gmail.com</t>
+  </si>
+  <si>
+    <t>Aldo Sarapura</t>
+  </si>
+  <si>
+    <t>losyacones71@gmail.com</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento Puesto San Cayetano.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puesto San Cayetano </t>
+  </si>
+  <si>
+    <t>Joaquin V. Gonzalez (Salta Forestal)</t>
+  </si>
+  <si>
+    <t>Artemio Soria (4 familias, Cornu, Soria, Vizgarra)</t>
+  </si>
+  <si>
+    <t>Edgardo Sandez</t>
+  </si>
+  <si>
+    <t>sandez.edgardo@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Balboa</t>
+  </si>
+  <si>
+    <t>Anta</t>
+  </si>
+  <si>
+    <t>Metán</t>
+  </si>
+  <si>
+    <t>Rosario de Lerma</t>
+  </si>
+  <si>
+    <t>Rosario de la Frontera</t>
+  </si>
+  <si>
+    <t>Guachipas</t>
   </si>
 </sst>
 </file>
@@ -519,7 +756,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -533,6 +770,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -835,16 +1076,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="54.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" customWidth="1"/>
     <col min="4" max="4" width="49.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1796875" customWidth="1"/>
-    <col min="8" max="8" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="17.453125" style="6" customWidth="1"/>
     <col min="9" max="9" width="34.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="40.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.08984375" bestFit="1" customWidth="1"/>
@@ -858,11 +1099,11 @@
     <col min="19" max="19" width="14.08984375" customWidth="1"/>
     <col min="20" max="20" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="33.90625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="40.36328125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="28.36328125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.1796875" customWidth="1"/>
     <col min="27" max="27" width="17.26953125" customWidth="1"/>
     <col min="28" max="28" width="26" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14" bestFit="1" customWidth="1"/>
@@ -891,7 +1132,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -983,7 +1224,7 @@
       <c r="G2" t="s">
         <v>110</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I2" t="s">
@@ -1075,7 +1316,7 @@
       <c r="G3" t="s">
         <v>45</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I3" t="s">
@@ -1167,7 +1408,7 @@
       <c r="G4" t="s">
         <v>45</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I4" t="s">
@@ -1244,7 +1485,7 @@
       <c r="G5" t="s">
         <v>45</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I5" t="s">
@@ -1336,7 +1577,7 @@
       <c r="G6" t="s">
         <v>110</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I6" t="s">
@@ -1416,7 +1657,7 @@
       <c r="G7" t="s">
         <v>110</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I7" t="s">
@@ -1508,7 +1749,7 @@
       <c r="G8" t="s">
         <v>110</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I8" t="s">
@@ -1600,7 +1841,7 @@
       <c r="G9" t="s">
         <v>110</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I9" t="s">
@@ -1692,7 +1933,7 @@
       <c r="G10" t="s">
         <v>110</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I10" t="s">
@@ -1784,7 +2025,7 @@
       <c r="G11" t="s">
         <v>110</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I11" t="s">
@@ -1876,7 +2117,7 @@
       <c r="G12" t="s">
         <v>110</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I12" t="s">
@@ -1968,7 +2209,7 @@
       <c r="G13" t="s">
         <v>110</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I13" t="s">
@@ -2060,7 +2301,7 @@
       <c r="G14" t="s">
         <v>110</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I14" t="s">
@@ -2152,7 +2393,7 @@
       <c r="G15" t="s">
         <v>110</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I15" t="s">
@@ -2220,6 +2461,727 @@
       </c>
       <c r="AD15">
         <v>-63.065199999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J16" t="s">
+        <v>142</v>
+      </c>
+      <c r="K16">
+        <v>340</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>120</v>
+      </c>
+      <c r="Q16">
+        <v>15</v>
+      </c>
+      <c r="R16" t="s">
+        <v>49</v>
+      </c>
+      <c r="S16" t="s">
+        <v>143</v>
+      </c>
+      <c r="T16" t="s">
+        <v>50</v>
+      </c>
+      <c r="U16" t="s">
+        <v>144</v>
+      </c>
+      <c r="V16" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16">
+        <v>3874126060</v>
+      </c>
+      <c r="X16" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA16">
+        <v>3874024259</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC16">
+        <v>-25.692167000000001</v>
+      </c>
+      <c r="AD16">
+        <v>-65.493860999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" t="s">
+        <v>214</v>
+      </c>
+      <c r="G17" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" t="s">
+        <v>152</v>
+      </c>
+      <c r="J17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K17">
+        <v>390</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>300</v>
+      </c>
+      <c r="Q17">
+        <v>300</v>
+      </c>
+      <c r="R17" t="s">
+        <v>48</v>
+      </c>
+      <c r="S17" t="s">
+        <v>143</v>
+      </c>
+      <c r="T17" t="s">
+        <v>49</v>
+      </c>
+      <c r="U17" t="s">
+        <v>154</v>
+      </c>
+      <c r="V17" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17">
+        <v>3872535050</v>
+      </c>
+      <c r="X17" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA17">
+        <v>3874863348</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC17">
+        <v>-25.012886000000002</v>
+      </c>
+      <c r="AD17">
+        <v>-66.506309999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" t="s">
+        <v>162</v>
+      </c>
+      <c r="J18" t="s">
+        <v>163</v>
+      </c>
+      <c r="K18">
+        <v>430</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1131</v>
+      </c>
+      <c r="Q18">
+        <v>1131</v>
+      </c>
+      <c r="R18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S18" t="s">
+        <v>164</v>
+      </c>
+      <c r="T18" t="s">
+        <v>34</v>
+      </c>
+      <c r="U18" t="s">
+        <v>165</v>
+      </c>
+      <c r="V18" t="s">
+        <v>36</v>
+      </c>
+      <c r="W18">
+        <v>1168017605</v>
+      </c>
+      <c r="X18" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA18">
+        <v>3876455446</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC18">
+        <v>-26.104167</v>
+      </c>
+      <c r="AD18">
+        <v>-65.135000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" t="s">
+        <v>211</v>
+      </c>
+      <c r="F19" t="s">
+        <v>215</v>
+      </c>
+      <c r="G19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" t="s">
+        <v>173</v>
+      </c>
+      <c r="J19" t="s">
+        <v>174</v>
+      </c>
+      <c r="K19">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>12</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>300</v>
+      </c>
+      <c r="Q19">
+        <v>300</v>
+      </c>
+      <c r="R19" t="s">
+        <v>33</v>
+      </c>
+      <c r="S19" t="s">
+        <v>164</v>
+      </c>
+      <c r="T19" t="s">
+        <v>50</v>
+      </c>
+      <c r="U19" t="s">
+        <v>165</v>
+      </c>
+      <c r="V19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W19">
+        <v>1168017605</v>
+      </c>
+      <c r="X19" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA19">
+        <v>3876455446</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC19">
+        <v>-25.833888999999999</v>
+      </c>
+      <c r="AD19">
+        <v>-64.849166999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" t="s">
+        <v>213</v>
+      </c>
+      <c r="G20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" t="s">
+        <v>179</v>
+      </c>
+      <c r="J20" t="s">
+        <v>180</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>30</v>
+      </c>
+      <c r="M20">
+        <v>25</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>100</v>
+      </c>
+      <c r="Q20">
+        <v>20</v>
+      </c>
+      <c r="R20" t="s">
+        <v>48</v>
+      </c>
+      <c r="S20" t="s">
+        <v>143</v>
+      </c>
+      <c r="T20" t="s">
+        <v>50</v>
+      </c>
+      <c r="U20" t="s">
+        <v>181</v>
+      </c>
+      <c r="V20" t="s">
+        <v>36</v>
+      </c>
+      <c r="W20">
+        <v>3876517136</v>
+      </c>
+      <c r="X20" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA20">
+        <v>3876452323</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC20">
+        <v>-25.584311</v>
+      </c>
+      <c r="AD20">
+        <v>-63.990313999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" t="s">
+        <v>212</v>
+      </c>
+      <c r="G21" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" t="s">
+        <v>188</v>
+      </c>
+      <c r="J21" t="s">
+        <v>189</v>
+      </c>
+      <c r="K21">
+        <v>40</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1500</v>
+      </c>
+      <c r="Q21">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>49</v>
+      </c>
+      <c r="S21" t="s">
+        <v>143</v>
+      </c>
+      <c r="T21" t="s">
+        <v>50</v>
+      </c>
+      <c r="U21" t="s">
+        <v>190</v>
+      </c>
+      <c r="V21" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21">
+        <v>3876417553</v>
+      </c>
+      <c r="X21" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA21">
+        <v>3874105178</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F22" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" t="s">
+        <v>197</v>
+      </c>
+      <c r="J22" t="s">
+        <v>198</v>
+      </c>
+      <c r="K22">
+        <v>1800</v>
+      </c>
+      <c r="L22">
+        <v>1000</v>
+      </c>
+      <c r="M22">
+        <v>500</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>10000</v>
+      </c>
+      <c r="R22" t="s">
+        <v>199</v>
+      </c>
+      <c r="S22" t="s">
+        <v>164</v>
+      </c>
+      <c r="T22" t="s">
+        <v>49</v>
+      </c>
+      <c r="U22" t="s">
+        <v>200</v>
+      </c>
+      <c r="V22" t="s">
+        <v>201</v>
+      </c>
+      <c r="W22">
+        <v>3874039856</v>
+      </c>
+      <c r="X22" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA22">
+        <v>3875100237</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC22">
+        <v>-24.618037580510201</v>
+      </c>
+      <c r="AD22">
+        <v>-65.3853896488462</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>205</v>
+      </c>
+      <c r="C23" t="s">
+        <v>206</v>
+      </c>
+      <c r="D23" t="s">
+        <v>207</v>
+      </c>
+      <c r="E23" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" t="s">
+        <v>212</v>
+      </c>
+      <c r="G23" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" t="s">
+        <v>208</v>
+      </c>
+      <c r="J23">
+        <v>700</v>
+      </c>
+      <c r="K23">
+        <v>700</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>4800</v>
+      </c>
+      <c r="Q23">
+        <v>15</v>
+      </c>
+      <c r="R23" t="s">
+        <v>49</v>
+      </c>
+      <c r="S23" t="s">
+        <v>143</v>
+      </c>
+      <c r="T23" t="s">
+        <v>50</v>
+      </c>
+      <c r="U23" t="s">
+        <v>192</v>
+      </c>
+      <c r="V23" t="s">
+        <v>36</v>
+      </c>
+      <c r="W23">
+        <v>3874105178</v>
+      </c>
+      <c r="X23" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA23">
+        <v>3872509737</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49018934-BDD4-4D0C-93BC-FA66DD187F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B3AB62-A4BE-421A-99D1-4E9763E6C1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3008,6 +3008,12 @@
       <c r="AB21" t="s">
         <v>193</v>
       </c>
+      <c r="AC21">
+        <v>-24.845064061599899</v>
+      </c>
+      <c r="AD21">
+        <v>-63.3651513354</v>
+      </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22">
@@ -3182,6 +3188,12 @@
       </c>
       <c r="AB23" t="s">
         <v>210</v>
+      </c>
+      <c r="AC23">
+        <v>-24.719692255799899</v>
+      </c>
+      <c r="AD23">
+        <v>-63.582719593999897</v>
       </c>
     </row>
   </sheetData>

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B3AB62-A4BE-421A-99D1-4E9763E6C1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47524BB-9689-489D-ABCF-07E1E1B9DA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2644,7 +2644,7 @@
         <v>-25.012886000000002</v>
       </c>
       <c r="AD17">
-        <v>-66.506309999999999</v>
+        <v>-65.650631000000004</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.35">

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47524BB-9689-489D-ABCF-07E1E1B9DA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B0817A-1040-41D4-9D23-7D27DEC310A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="229">
   <si>
     <t>archivo_origen</t>
   </si>
@@ -675,6 +675,42 @@
   </si>
   <si>
     <t>Guachipas</t>
+  </si>
+  <si>
+    <t>PATChaco - Ficha de Relevamiento Finca Santa Anita.xlsx</t>
+  </si>
+  <si>
+    <t>Coronel Moldes</t>
+  </si>
+  <si>
+    <t>Salta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos Lewis , Valentina chavez , Julian Lewis </t>
+  </si>
+  <si>
+    <t>20 vacas , 60 cabras , 8 caballos</t>
+  </si>
+  <si>
+    <t>Rafael Saldaño</t>
+  </si>
+  <si>
+    <t>bernasaldanio@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernanda rios </t>
+  </si>
+  <si>
+    <t>ferndariosinta@gmail.com</t>
+  </si>
+  <si>
+    <t>Finca Santa Anita - Piedras Moradas</t>
+  </si>
+  <si>
+    <t>La Viña</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Piedras Moradas  - Coronel Moldes</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="54.90625" bestFit="1" customWidth="1"/>
@@ -3196,6 +3232,98 @@
         <v>-63.582719593999897</v>
       </c>
     </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E24" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" t="s">
+        <v>227</v>
+      </c>
+      <c r="G24" t="s">
+        <v>219</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" t="s">
+        <v>220</v>
+      </c>
+      <c r="J24" t="s">
+        <v>221</v>
+      </c>
+      <c r="K24">
+        <v>20</v>
+      </c>
+      <c r="L24">
+        <v>60</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>8</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>55</v>
+      </c>
+      <c r="Q24">
+        <v>50</v>
+      </c>
+      <c r="R24" t="s">
+        <v>164</v>
+      </c>
+      <c r="S24" t="s">
+        <v>164</v>
+      </c>
+      <c r="T24" t="s">
+        <v>50</v>
+      </c>
+      <c r="U24" t="s">
+        <v>222</v>
+      </c>
+      <c r="V24" t="s">
+        <v>36</v>
+      </c>
+      <c r="W24">
+        <v>3874024259</v>
+      </c>
+      <c r="X24" t="s">
+        <v>223</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>224</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA24">
+        <v>3874126060</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC24">
+        <v>-25.291271999999999</v>
+      </c>
+      <c r="AD24">
+        <v>-65.461913999999993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B0817A-1040-41D4-9D23-7D27DEC310A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CDF98F-932F-4FCE-9696-B6C422E5CF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="326">
   <si>
     <t>archivo_origen</t>
   </si>
@@ -711,13 +711,304 @@
   </si>
   <si>
     <t xml:space="preserve"> Piedras Moradas  - Coronel Moldes</t>
+  </si>
+  <si>
+    <t>el arbolito.xlsx</t>
+  </si>
+  <si>
+    <t>El Arbolito</t>
+  </si>
+  <si>
+    <t>La Cabral, La Cabral, San Cristóbal, Santa Fe</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Rubén Paz</t>
+  </si>
+  <si>
+    <t>68 vacunos</t>
+  </si>
+  <si>
+    <t>Sebastián Valiente</t>
+  </si>
+  <si>
+    <t>valiente.sebastián@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Jorge Marcelo Pisani</t>
+  </si>
+  <si>
+    <t>pisani.jorge@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>el refugio.xlsx</t>
+  </si>
+  <si>
+    <t>El Refugio</t>
+  </si>
+  <si>
+    <t>Tostado, 9 de Julio, Santa Fe</t>
+  </si>
+  <si>
+    <t>Stella Maris Vicentín</t>
+  </si>
+  <si>
+    <t>140 vacunos, 23 ovinos,19  caprinos</t>
+  </si>
+  <si>
+    <t>César G. Castro</t>
+  </si>
+  <si>
+    <t>castro.cesargerman@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Claudia Vidal</t>
+  </si>
+  <si>
+    <t>vidal.claudia@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>elsolitario.xlsx</t>
+  </si>
+  <si>
+    <t>El Solitario</t>
+  </si>
+  <si>
+    <t>Estancia La Florencia, Municipio Ingeniero Juárez, Derpartmento Matacos, Provincia de Formosa</t>
+  </si>
+  <si>
+    <t>Robustiano Saravia</t>
+  </si>
+  <si>
+    <t>50 vacunos, 150 cabras, 25 ovejas, 30 cerdos</t>
+  </si>
+  <si>
+    <t>Mario Cordoba</t>
+  </si>
+  <si>
+    <t>cordoba.marioa@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Patricio Sanz</t>
+  </si>
+  <si>
+    <t>sanz.patricio@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>guayacanal.xlsx</t>
+  </si>
+  <si>
+    <t>El Guayacanal</t>
+  </si>
+  <si>
+    <t>Zona de El Rosillo, Municipio Ingeniero Juarez, departamento Matacos, Provincia de Formosa</t>
+  </si>
+  <si>
+    <t>Emilio Parada</t>
+  </si>
+  <si>
+    <t>200 Vacunos</t>
+  </si>
+  <si>
+    <t>Patricio sanz</t>
+  </si>
+  <si>
+    <t>cordoba,marioa@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>la nueva palmira.xlsx</t>
+  </si>
+  <si>
+    <t>La Nueva Pamira</t>
+  </si>
+  <si>
+    <t>Capivara, San Cristóbal, Santa Fe</t>
+  </si>
+  <si>
+    <t>Asoc. Coop. EEA INTA Rafaela</t>
+  </si>
+  <si>
+    <t>600 vacunos</t>
+  </si>
+  <si>
+    <t>laposta.xlsx</t>
+  </si>
+  <si>
+    <t>CONCEPCION DEL BERMEJO</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SEBASTIAN, PABLO Y GUILLERMO DE ARRIORTUA</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDGARDO LEONHARDT </t>
+  </si>
+  <si>
+    <t>leonhardt.edgardo@inta.gov.ar</t>
+  </si>
+  <si>
+    <t>PALACIOS VERONICA</t>
+  </si>
+  <si>
+    <t>palacios.veronica@inta.gov.ar</t>
+  </si>
+  <si>
+    <t>larenga.xlsx</t>
+  </si>
+  <si>
+    <t>La Renga</t>
+  </si>
+  <si>
+    <t>Zona La Junta, departamento Matacos, provincia de Formosa</t>
+  </si>
+  <si>
+    <t>Eufemio Molina</t>
+  </si>
+  <si>
+    <t>150 bovinos, 50 cabras</t>
+  </si>
+  <si>
+    <t>ojo de aguila.xlsx</t>
+  </si>
+  <si>
+    <t>Ojo de Águila</t>
+  </si>
+  <si>
+    <t>El Araza, Gral. Obligado, Santa Fe</t>
+  </si>
+  <si>
+    <t>Augusto Gastaldo</t>
+  </si>
+  <si>
+    <t>300 vacunos, 20 ovinos</t>
+  </si>
+  <si>
+    <t>No formal</t>
+  </si>
+  <si>
+    <t>Fernando Brandalise</t>
+  </si>
+  <si>
+    <t>brandalise.fernando@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>rosafarias.xlsx</t>
+  </si>
+  <si>
+    <t>Rosa Farías</t>
+  </si>
+  <si>
+    <t>Santa Felicia, Vera, Santa Fe</t>
+  </si>
+  <si>
+    <t>44 vacunos</t>
+  </si>
+  <si>
+    <t>Roberto Reynares</t>
+  </si>
+  <si>
+    <t>reynares.roberto@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>rubensaravia.xlsx</t>
+  </si>
+  <si>
+    <t>Ruben Saravia</t>
+  </si>
+  <si>
+    <t>Villa Guillermina, Gral. Obligado, Santa Fe</t>
+  </si>
+  <si>
+    <t>85 vacunos, 15 ovinos, 15 caprinos</t>
+  </si>
+  <si>
+    <t>Carlos María Espíndola</t>
+  </si>
+  <si>
+    <t>espindola.carlos@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Romina Beltrán</t>
+  </si>
+  <si>
+    <t>CONICET</t>
+  </si>
+  <si>
+    <t>beltran.romina@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>La Posta de los Bascos</t>
+  </si>
+  <si>
+    <t>San Cristóbal</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>Tostado</t>
+  </si>
+  <si>
+    <t>9 de Julio</t>
+  </si>
+  <si>
+    <t>Estancia La Florencia, Municipio Ingeniero Juárez</t>
+  </si>
+  <si>
+    <t>Matacos</t>
+  </si>
+  <si>
+    <t>Formosa</t>
+  </si>
+  <si>
+    <t>Zona de El Rosillo, Municipio Ingeniero Juarez</t>
+  </si>
+  <si>
+    <t>Capivara</t>
+  </si>
+  <si>
+    <t>Concepción del Bermejo</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Chaco</t>
+  </si>
+  <si>
+    <t>Zona La Junta</t>
+  </si>
+  <si>
+    <t>El Araza</t>
+  </si>
+  <si>
+    <t>Gral. Obligado</t>
+  </si>
+  <si>
+    <t>Santa Felicia</t>
+  </si>
+  <si>
+    <t>Vera</t>
+  </si>
+  <si>
+    <t>Villa Guillermina</t>
+  </si>
+  <si>
+    <t>La Cabral</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,16 +1021,32 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+        <bgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -788,11 +1095,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -810,6 +1132,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1112,13 +1446,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="54.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.81640625" customWidth="1"/>
-    <col min="4" max="4" width="49.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1796875" customWidth="1"/>
     <col min="8" max="8" width="17.453125" style="6" customWidth="1"/>
@@ -3324,6 +3657,863 @@
         <v>-65.461913999999993</v>
       </c>
     </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>229</v>
+      </c>
+      <c r="C25" t="s">
+        <v>230</v>
+      </c>
+      <c r="D25" t="s">
+        <v>231</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I25" t="s">
+        <v>233</v>
+      </c>
+      <c r="J25" t="s">
+        <v>234</v>
+      </c>
+      <c r="K25" s="9">
+        <v>68</v>
+      </c>
+      <c r="L25" s="9">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9">
+        <v>0</v>
+      </c>
+      <c r="O25" s="9">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>119</v>
+      </c>
+      <c r="Q25">
+        <v>119</v>
+      </c>
+      <c r="R25" t="s">
+        <v>48</v>
+      </c>
+      <c r="S25" t="s">
+        <v>48</v>
+      </c>
+      <c r="T25" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" t="s">
+        <v>235</v>
+      </c>
+      <c r="V25" t="s">
+        <v>36</v>
+      </c>
+      <c r="W25">
+        <v>3408671684</v>
+      </c>
+      <c r="X25" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA25">
+        <v>3492519730</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>239</v>
+      </c>
+      <c r="C26" t="s">
+        <v>240</v>
+      </c>
+      <c r="D26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I26" t="s">
+        <v>242</v>
+      </c>
+      <c r="J26" t="s">
+        <v>243</v>
+      </c>
+      <c r="K26" s="10">
+        <v>140</v>
+      </c>
+      <c r="L26" s="10">
+        <v>19</v>
+      </c>
+      <c r="M26" s="10">
+        <v>23</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0</v>
+      </c>
+      <c r="O26" s="10">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>202</v>
+      </c>
+      <c r="Q26">
+        <v>202</v>
+      </c>
+      <c r="R26" t="s">
+        <v>48</v>
+      </c>
+      <c r="S26" t="s">
+        <v>48</v>
+      </c>
+      <c r="T26" t="s">
+        <v>34</v>
+      </c>
+      <c r="U26" t="s">
+        <v>244</v>
+      </c>
+      <c r="V26" t="s">
+        <v>36</v>
+      </c>
+      <c r="W26">
+        <v>3482574888</v>
+      </c>
+      <c r="X26" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA26">
+        <v>3482510304</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" t="s">
+        <v>249</v>
+      </c>
+      <c r="D27" t="s">
+        <v>250</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" t="s">
+        <v>251</v>
+      </c>
+      <c r="J27" t="s">
+        <v>252</v>
+      </c>
+      <c r="K27" s="9">
+        <v>50</v>
+      </c>
+      <c r="L27" s="9">
+        <v>150</v>
+      </c>
+      <c r="M27" s="9">
+        <v>25</v>
+      </c>
+      <c r="N27" s="9">
+        <v>0</v>
+      </c>
+      <c r="O27" s="9">
+        <v>30</v>
+      </c>
+      <c r="P27">
+        <v>500</v>
+      </c>
+      <c r="Q27">
+        <v>500</v>
+      </c>
+      <c r="R27" t="s">
+        <v>164</v>
+      </c>
+      <c r="S27" t="s">
+        <v>164</v>
+      </c>
+      <c r="T27" t="s">
+        <v>49</v>
+      </c>
+      <c r="U27" t="s">
+        <v>253</v>
+      </c>
+      <c r="V27" t="s">
+        <v>36</v>
+      </c>
+      <c r="W27">
+        <v>3715616068</v>
+      </c>
+      <c r="X27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA27">
+        <v>1168020312</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" t="s">
+        <v>258</v>
+      </c>
+      <c r="D28" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" t="s">
+        <v>260</v>
+      </c>
+      <c r="J28" t="s">
+        <v>261</v>
+      </c>
+      <c r="K28" s="10">
+        <v>200</v>
+      </c>
+      <c r="L28" s="10">
+        <v>0</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0</v>
+      </c>
+      <c r="N28" s="10">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1500</v>
+      </c>
+      <c r="Q28">
+        <v>1300</v>
+      </c>
+      <c r="R28" t="s">
+        <v>164</v>
+      </c>
+      <c r="S28" t="s">
+        <v>164</v>
+      </c>
+      <c r="T28" t="s">
+        <v>49</v>
+      </c>
+      <c r="U28" t="s">
+        <v>262</v>
+      </c>
+      <c r="V28" t="s">
+        <v>36</v>
+      </c>
+      <c r="W28">
+        <v>1168020312</v>
+      </c>
+      <c r="X28" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA28">
+        <v>3715616068</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>264</v>
+      </c>
+      <c r="C29" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" t="s">
+        <v>266</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I29" t="s">
+        <v>267</v>
+      </c>
+      <c r="J29" t="s">
+        <v>268</v>
+      </c>
+      <c r="K29" s="9">
+        <v>600</v>
+      </c>
+      <c r="L29" s="9">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9">
+        <v>0</v>
+      </c>
+      <c r="O29" s="9">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>597</v>
+      </c>
+      <c r="Q29">
+        <v>597</v>
+      </c>
+      <c r="R29" t="s">
+        <v>48</v>
+      </c>
+      <c r="S29" t="s">
+        <v>48</v>
+      </c>
+      <c r="T29" t="s">
+        <v>34</v>
+      </c>
+      <c r="U29" t="s">
+        <v>235</v>
+      </c>
+      <c r="V29" t="s">
+        <v>36</v>
+      </c>
+      <c r="W29">
+        <v>3408671684</v>
+      </c>
+      <c r="X29" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA29">
+        <v>3492519730</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C30" t="s">
+        <v>306</v>
+      </c>
+      <c r="D30" t="s">
+        <v>270</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="I30" t="s">
+        <v>272</v>
+      </c>
+      <c r="J30">
+        <v>1400</v>
+      </c>
+      <c r="K30" s="10">
+        <v>1400</v>
+      </c>
+      <c r="L30" s="10">
+        <v>0</v>
+      </c>
+      <c r="M30" s="10">
+        <v>0</v>
+      </c>
+      <c r="N30" s="10">
+        <v>0</v>
+      </c>
+      <c r="O30" s="10">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1095</v>
+      </c>
+      <c r="Q30">
+        <v>600</v>
+      </c>
+      <c r="R30" t="s">
+        <v>273</v>
+      </c>
+      <c r="S30" t="s">
+        <v>49</v>
+      </c>
+      <c r="T30" t="s">
+        <v>34</v>
+      </c>
+      <c r="U30" t="s">
+        <v>274</v>
+      </c>
+      <c r="V30" t="s">
+        <v>36</v>
+      </c>
+      <c r="W30">
+        <v>3644354666</v>
+      </c>
+      <c r="X30" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA30">
+        <v>1130212806</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C31" t="s">
+        <v>279</v>
+      </c>
+      <c r="D31" t="s">
+        <v>280</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" t="s">
+        <v>281</v>
+      </c>
+      <c r="J31" t="s">
+        <v>282</v>
+      </c>
+      <c r="K31" s="9">
+        <v>150</v>
+      </c>
+      <c r="L31" s="9">
+        <v>50</v>
+      </c>
+      <c r="M31" s="9">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9">
+        <v>0</v>
+      </c>
+      <c r="O31" s="9">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>1000</v>
+      </c>
+      <c r="Q31">
+        <v>1000</v>
+      </c>
+      <c r="R31" t="s">
+        <v>33</v>
+      </c>
+      <c r="S31" t="s">
+        <v>33</v>
+      </c>
+      <c r="T31" t="s">
+        <v>49</v>
+      </c>
+      <c r="U31" t="s">
+        <v>255</v>
+      </c>
+      <c r="V31" t="s">
+        <v>36</v>
+      </c>
+      <c r="W31">
+        <v>1168020312</v>
+      </c>
+      <c r="X31" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA31">
+        <v>3715616068</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>283</v>
+      </c>
+      <c r="C32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I32" t="s">
+        <v>286</v>
+      </c>
+      <c r="J32" t="s">
+        <v>287</v>
+      </c>
+      <c r="K32" s="10">
+        <v>300</v>
+      </c>
+      <c r="L32" s="10">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10">
+        <v>20</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0</v>
+      </c>
+      <c r="O32" s="10">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>836</v>
+      </c>
+      <c r="Q32">
+        <v>836</v>
+      </c>
+      <c r="R32" t="s">
+        <v>48</v>
+      </c>
+      <c r="S32" t="s">
+        <v>48</v>
+      </c>
+      <c r="T32" t="s">
+        <v>288</v>
+      </c>
+      <c r="U32" t="s">
+        <v>244</v>
+      </c>
+      <c r="V32" t="s">
+        <v>36</v>
+      </c>
+      <c r="W32">
+        <v>3482574888</v>
+      </c>
+      <c r="X32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA32">
+        <v>3483408310</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>291</v>
+      </c>
+      <c r="C33" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" t="s">
+        <v>293</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I33" t="s">
+        <v>292</v>
+      </c>
+      <c r="J33" t="s">
+        <v>294</v>
+      </c>
+      <c r="K33" s="9">
+        <v>44</v>
+      </c>
+      <c r="L33" s="9">
+        <v>0</v>
+      </c>
+      <c r="M33" s="9">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9">
+        <v>0</v>
+      </c>
+      <c r="O33" s="9">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>50</v>
+      </c>
+      <c r="Q33">
+        <v>50</v>
+      </c>
+      <c r="R33" t="s">
+        <v>48</v>
+      </c>
+      <c r="S33" t="s">
+        <v>48</v>
+      </c>
+      <c r="T33" t="s">
+        <v>34</v>
+      </c>
+      <c r="U33" t="s">
+        <v>295</v>
+      </c>
+      <c r="V33" t="s">
+        <v>36</v>
+      </c>
+      <c r="W33">
+        <v>3482322533</v>
+      </c>
+      <c r="X33" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA33">
+        <v>3482510304</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>297</v>
+      </c>
+      <c r="C34" t="s">
+        <v>298</v>
+      </c>
+      <c r="D34" t="s">
+        <v>299</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I34" t="s">
+        <v>298</v>
+      </c>
+      <c r="J34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K34" s="10">
+        <v>85</v>
+      </c>
+      <c r="L34" s="10">
+        <v>15</v>
+      </c>
+      <c r="M34" s="10">
+        <v>15</v>
+      </c>
+      <c r="N34" s="10">
+        <v>0</v>
+      </c>
+      <c r="O34" s="10">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>266</v>
+      </c>
+      <c r="Q34">
+        <v>266</v>
+      </c>
+      <c r="R34" t="s">
+        <v>48</v>
+      </c>
+      <c r="T34" t="s">
+        <v>34</v>
+      </c>
+      <c r="U34" t="s">
+        <v>301</v>
+      </c>
+      <c r="V34" t="s">
+        <v>36</v>
+      </c>
+      <c r="W34">
+        <v>3794246610</v>
+      </c>
+      <c r="X34" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>304</v>
+      </c>
+      <c r="AA34">
+        <v>3458456470</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CDF98F-932F-4FCE-9696-B6C422E5CF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822331AB-DE39-484E-AB8B-6BE6722FFA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="325">
   <si>
     <t>archivo_origen</t>
   </si>
@@ -681,9 +681,6 @@
   </si>
   <si>
     <t>Coronel Moldes</t>
-  </si>
-  <si>
-    <t>Salta.</t>
   </si>
   <si>
     <t xml:space="preserve">Carlos Lewis , Valentina chavez , Julian Lewis </t>
@@ -3573,28 +3570,28 @@
         <v>217</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
         <v>218</v>
       </c>
       <c r="F24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G24" t="s">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J24" t="s">
         <v>220</v>
-      </c>
-      <c r="J24" t="s">
-        <v>221</v>
       </c>
       <c r="K24">
         <v>20</v>
@@ -3627,7 +3624,7 @@
         <v>50</v>
       </c>
       <c r="U24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="V24" t="s">
         <v>36</v>
@@ -3636,10 +3633,10 @@
         <v>3874024259</v>
       </c>
       <c r="X24" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y24" t="s">
         <v>223</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>224</v>
       </c>
       <c r="Z24" t="s">
         <v>36</v>
@@ -3648,7 +3645,7 @@
         <v>3874126060</v>
       </c>
       <c r="AB24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AC24">
         <v>-25.291271999999999</v>
@@ -3662,31 +3659,31 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" t="s">
         <v>229</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>230</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" t="s">
         <v>232</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>233</v>
-      </c>
-      <c r="J25" t="s">
-        <v>234</v>
       </c>
       <c r="K25" s="9">
         <v>68</v>
@@ -3719,7 +3716,7 @@
         <v>34</v>
       </c>
       <c r="U25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V25" t="s">
         <v>36</v>
@@ -3728,10 +3725,10 @@
         <v>3408671684</v>
       </c>
       <c r="X25" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y25" t="s">
         <v>236</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>237</v>
       </c>
       <c r="Z25" t="s">
         <v>36</v>
@@ -3740,7 +3737,7 @@
         <v>3492519730</v>
       </c>
       <c r="AB25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.35">
@@ -3748,31 +3745,31 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" t="s">
         <v>239</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>240</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I26" t="s">
         <v>241</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>242</v>
-      </c>
-      <c r="J26" t="s">
-        <v>243</v>
       </c>
       <c r="K26" s="10">
         <v>140</v>
@@ -3805,7 +3802,7 @@
         <v>34</v>
       </c>
       <c r="U26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V26" t="s">
         <v>36</v>
@@ -3814,10 +3811,10 @@
         <v>3482574888</v>
       </c>
       <c r="X26" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y26" t="s">
         <v>245</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>246</v>
       </c>
       <c r="Z26" t="s">
         <v>36</v>
@@ -3826,7 +3823,7 @@
         <v>3482510304</v>
       </c>
       <c r="AB26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.35">
@@ -3834,31 +3831,31 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" t="s">
         <v>248</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>249</v>
       </c>
-      <c r="D27" t="s">
-        <v>250</v>
-      </c>
       <c r="E27" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>313</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I27" t="s">
+        <v>250</v>
+      </c>
+      <c r="J27" t="s">
         <v>251</v>
-      </c>
-      <c r="J27" t="s">
-        <v>252</v>
       </c>
       <c r="K27" s="9">
         <v>50</v>
@@ -3891,7 +3888,7 @@
         <v>49</v>
       </c>
       <c r="U27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="V27" t="s">
         <v>36</v>
@@ -3900,10 +3897,10 @@
         <v>3715616068</v>
       </c>
       <c r="X27" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y27" t="s">
         <v>254</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>255</v>
       </c>
       <c r="Z27" t="s">
         <v>36</v>
@@ -3912,7 +3909,7 @@
         <v>1168020312</v>
       </c>
       <c r="AB27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.35">
@@ -3920,31 +3917,31 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" t="s">
         <v>257</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>258</v>
       </c>
-      <c r="D28" t="s">
-        <v>259</v>
-      </c>
       <c r="E28" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F28" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>312</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>313</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I28" t="s">
+        <v>259</v>
+      </c>
+      <c r="J28" t="s">
         <v>260</v>
-      </c>
-      <c r="J28" t="s">
-        <v>261</v>
       </c>
       <c r="K28" s="10">
         <v>200</v>
@@ -3977,7 +3974,7 @@
         <v>49</v>
       </c>
       <c r="U28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V28" t="s">
         <v>36</v>
@@ -3986,10 +3983,10 @@
         <v>1168020312</v>
       </c>
       <c r="X28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Y28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z28" t="s">
         <v>36</v>
@@ -3998,7 +3995,7 @@
         <v>3715616068</v>
       </c>
       <c r="AB28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.35">
@@ -4006,31 +4003,31 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" t="s">
         <v>264</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>265</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I29" t="s">
         <v>266</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>267</v>
-      </c>
-      <c r="J29" t="s">
-        <v>268</v>
       </c>
       <c r="K29" s="9">
         <v>600</v>
@@ -4063,7 +4060,7 @@
         <v>34</v>
       </c>
       <c r="U29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V29" t="s">
         <v>36</v>
@@ -4072,10 +4069,10 @@
         <v>3408671684</v>
       </c>
       <c r="X29" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y29" t="s">
         <v>236</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>237</v>
       </c>
       <c r="Z29" t="s">
         <v>36</v>
@@ -4084,7 +4081,7 @@
         <v>3492519730</v>
       </c>
       <c r="AB29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.35">
@@ -4092,28 +4089,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>268</v>
+      </c>
+      <c r="C30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" t="s">
         <v>269</v>
       </c>
-      <c r="C30" t="s">
-        <v>306</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="I30" t="s">
         <v>271</v>
-      </c>
-      <c r="I30" t="s">
-        <v>272</v>
       </c>
       <c r="J30">
         <v>1400</v>
@@ -4140,7 +4137,7 @@
         <v>600</v>
       </c>
       <c r="R30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S30" t="s">
         <v>49</v>
@@ -4149,7 +4146,7 @@
         <v>34</v>
       </c>
       <c r="U30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="V30" t="s">
         <v>36</v>
@@ -4158,10 +4155,10 @@
         <v>3644354666</v>
       </c>
       <c r="X30" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y30" t="s">
         <v>275</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>276</v>
       </c>
       <c r="Z30" t="s">
         <v>36</v>
@@ -4170,7 +4167,7 @@
         <v>1130212806</v>
       </c>
       <c r="AB30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.35">
@@ -4178,31 +4175,31 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>277</v>
+      </c>
+      <c r="C31" t="s">
         <v>278</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>279</v>
       </c>
-      <c r="D31" t="s">
-        <v>280</v>
-      </c>
       <c r="E31" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F31" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>313</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I31" t="s">
+        <v>280</v>
+      </c>
+      <c r="J31" t="s">
         <v>281</v>
-      </c>
-      <c r="J31" t="s">
-        <v>282</v>
       </c>
       <c r="K31" s="9">
         <v>150</v>
@@ -4235,7 +4232,7 @@
         <v>49</v>
       </c>
       <c r="U31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V31" t="s">
         <v>36</v>
@@ -4244,10 +4241,10 @@
         <v>1168020312</v>
       </c>
       <c r="X31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Y31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z31" t="s">
         <v>36</v>
@@ -4256,7 +4253,7 @@
         <v>3715616068</v>
       </c>
       <c r="AB31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.35">
@@ -4264,31 +4261,31 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>282</v>
+      </c>
+      <c r="C32" t="s">
         <v>283</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>284</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I32" t="s">
         <v>285</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>286</v>
-      </c>
-      <c r="J32" t="s">
-        <v>287</v>
       </c>
       <c r="K32" s="10">
         <v>300</v>
@@ -4318,10 +4315,10 @@
         <v>48</v>
       </c>
       <c r="T32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="U32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V32" t="s">
         <v>36</v>
@@ -4330,10 +4327,10 @@
         <v>3482574888</v>
       </c>
       <c r="X32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Y32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Z32" t="s">
         <v>36</v>
@@ -4342,7 +4339,7 @@
         <v>3483408310</v>
       </c>
       <c r="AB32" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.35">
@@ -4350,31 +4347,31 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>290</v>
+      </c>
+      <c r="C33" t="s">
         <v>291</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>292</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I33" t="s">
+        <v>291</v>
+      </c>
+      <c r="J33" t="s">
         <v>293</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I33" t="s">
-        <v>292</v>
-      </c>
-      <c r="J33" t="s">
-        <v>294</v>
       </c>
       <c r="K33" s="9">
         <v>44</v>
@@ -4407,7 +4404,7 @@
         <v>34</v>
       </c>
       <c r="U33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="V33" t="s">
         <v>36</v>
@@ -4416,10 +4413,10 @@
         <v>3482322533</v>
       </c>
       <c r="X33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y33" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z33" t="s">
         <v>36</v>
@@ -4428,7 +4425,7 @@
         <v>3482510304</v>
       </c>
       <c r="AB33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.35">
@@ -4436,31 +4433,31 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>296</v>
+      </c>
+      <c r="C34" t="s">
         <v>297</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>298</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I34" t="s">
+        <v>297</v>
+      </c>
+      <c r="J34" t="s">
         <v>299</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I34" t="s">
-        <v>298</v>
-      </c>
-      <c r="J34" t="s">
-        <v>300</v>
       </c>
       <c r="K34" s="10">
         <v>85</v>
@@ -4490,7 +4487,7 @@
         <v>34</v>
       </c>
       <c r="U34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V34" t="s">
         <v>36</v>
@@ -4499,19 +4496,19 @@
         <v>3794246610</v>
       </c>
       <c r="X34" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y34" t="s">
         <v>302</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="Z34" t="s">
         <v>303</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>304</v>
       </c>
       <c r="AA34">
         <v>3458456470</v>
       </c>
       <c r="AB34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822331AB-DE39-484E-AB8B-6BE6722FFA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB436403-15D9-4A74-AE3C-F8EF15165FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -845,9 +845,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t xml:space="preserve">EDGARDO LEONHARDT </t>
-  </si>
-  <si>
     <t>leonhardt.edgardo@inta.gov.ar</t>
   </si>
   <si>
@@ -999,6 +996,9 @@
   </si>
   <si>
     <t>La Cabral</t>
+  </si>
+  <si>
+    <t>Edgardo  Leonhardt</t>
   </si>
 </sst>
 </file>
@@ -3668,13 +3668,13 @@
         <v>230</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F25" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>307</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>231</v>
@@ -3754,13 +3754,13 @@
         <v>240</v>
       </c>
       <c r="E26" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>309</v>
-      </c>
       <c r="G26" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>231</v>
@@ -3840,13 +3840,13 @@
         <v>249</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>312</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>30</v>
@@ -3926,13 +3926,13 @@
         <v>258</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F28" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>311</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>312</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>30</v>
@@ -4012,13 +4012,13 @@
         <v>265</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F29" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>307</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>231</v>
@@ -4092,19 +4092,19 @@
         <v>268</v>
       </c>
       <c r="C30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D30" t="s">
         <v>269</v>
       </c>
       <c r="E30" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="G30" s="8" t="s">
         <v>316</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>270</v>
@@ -4146,7 +4146,7 @@
         <v>34</v>
       </c>
       <c r="U30" t="s">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="V30" t="s">
         <v>36</v>
@@ -4155,10 +4155,10 @@
         <v>3644354666</v>
       </c>
       <c r="X30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y30" t="s">
         <v>274</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>275</v>
       </c>
       <c r="Z30" t="s">
         <v>36</v>
@@ -4167,7 +4167,7 @@
         <v>1130212806</v>
       </c>
       <c r="AB30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.35">
@@ -4175,31 +4175,31 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>276</v>
+      </c>
+      <c r="C31" t="s">
         <v>277</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>278</v>
       </c>
-      <c r="D31" t="s">
-        <v>279</v>
-      </c>
       <c r="E31" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F31" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>312</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I31" t="s">
+        <v>279</v>
+      </c>
+      <c r="J31" t="s">
         <v>280</v>
-      </c>
-      <c r="J31" t="s">
-        <v>281</v>
       </c>
       <c r="K31" s="9">
         <v>150</v>
@@ -4261,31 +4261,31 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C32" t="s">
         <v>282</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>283</v>
       </c>
-      <c r="D32" t="s">
-        <v>284</v>
-      </c>
       <c r="E32" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>320</v>
-      </c>
       <c r="G32" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>231</v>
       </c>
       <c r="I32" t="s">
+        <v>284</v>
+      </c>
+      <c r="J32" t="s">
         <v>285</v>
-      </c>
-      <c r="J32" t="s">
-        <v>286</v>
       </c>
       <c r="K32" s="10">
         <v>300</v>
@@ -4315,7 +4315,7 @@
         <v>48</v>
       </c>
       <c r="T32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="U32" t="s">
         <v>243</v>
@@ -4330,7 +4330,7 @@
         <v>244</v>
       </c>
       <c r="Y32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Z32" t="s">
         <v>36</v>
@@ -4339,7 +4339,7 @@
         <v>3483408310</v>
       </c>
       <c r="AB32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.35">
@@ -4347,31 +4347,31 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>289</v>
+      </c>
+      <c r="C33" t="s">
         <v>290</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>291</v>
       </c>
-      <c r="D33" t="s">
-        <v>292</v>
-      </c>
       <c r="E33" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="G33" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>231</v>
       </c>
       <c r="I33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K33" s="9">
         <v>44</v>
@@ -4404,7 +4404,7 @@
         <v>34</v>
       </c>
       <c r="U33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="V33" t="s">
         <v>36</v>
@@ -4413,7 +4413,7 @@
         <v>3482322533</v>
       </c>
       <c r="X33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Y33" t="s">
         <v>245</v>
@@ -4433,31 +4433,31 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>295</v>
+      </c>
+      <c r="C34" t="s">
         <v>296</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>297</v>
       </c>
-      <c r="D34" t="s">
-        <v>298</v>
-      </c>
       <c r="E34" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>231</v>
       </c>
       <c r="I34" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J34" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K34" s="10">
         <v>85</v>
@@ -4487,7 +4487,7 @@
         <v>34</v>
       </c>
       <c r="U34" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V34" t="s">
         <v>36</v>
@@ -4496,19 +4496,19 @@
         <v>3794246610</v>
       </c>
       <c r="X34" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y34" t="s">
         <v>301</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="Z34" t="s">
         <v>302</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>303</v>
       </c>
       <c r="AA34">
         <v>3458456470</v>
       </c>
       <c r="AB34" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/Consolidado_Relevamientos.xlsx
+++ b/Consolidado_Relevamientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTA\PATChaco\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB436403-15D9-4A74-AE3C-F8EF15165FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB32E7F-CAA9-4755-B000-17C0116E33FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="324">
   <si>
     <t>archivo_origen</t>
   </si>
@@ -807,9 +807,6 @@
   </si>
   <si>
     <t>200 Vacunos</t>
-  </si>
-  <si>
-    <t>Patricio sanz</t>
   </si>
   <si>
     <t>cordoba,marioa@inta.gob.ar</t>
@@ -3668,13 +3665,13 @@
         <v>230</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F25" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>305</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>306</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>231</v>
@@ -3754,13 +3751,13 @@
         <v>240</v>
       </c>
       <c r="E26" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>308</v>
-      </c>
       <c r="G26" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>231</v>
@@ -3840,13 +3837,13 @@
         <v>249</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="7" t="s">
         <v>310</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>311</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>30</v>
@@ -3926,13 +3923,13 @@
         <v>258</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F28" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>310</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>311</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>30</v>
@@ -3974,7 +3971,7 @@
         <v>49</v>
       </c>
       <c r="U28" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="V28" t="s">
         <v>36</v>
@@ -3995,7 +3992,7 @@
         <v>3715616068</v>
       </c>
       <c r="AB28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.35">
@@ -4003,31 +4000,31 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>262</v>
+      </c>
+      <c r="C29" t="s">
         <v>263</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>264</v>
       </c>
-      <c r="D29" t="s">
-        <v>265</v>
-      </c>
       <c r="E29" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F29" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>305</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>306</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>231</v>
       </c>
       <c r="I29" t="s">
+        <v>265</v>
+      </c>
+      <c r="J29" t="s">
         <v>266</v>
-      </c>
-      <c r="J29" t="s">
-        <v>267</v>
       </c>
       <c r="K29" s="9">
         <v>600</v>
@@ -4089,28 +4086,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" t="s">
+        <v>303</v>
+      </c>
+      <c r="D30" t="s">
         <v>268</v>
       </c>
-      <c r="C30" t="s">
-        <v>304</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="I30" t="s">
         <v>270</v>
-      </c>
-      <c r="I30" t="s">
-        <v>271</v>
       </c>
       <c r="J30">
         <v>1400</v>
@@ -4137,7 +4134,7 @@
         <v>600</v>
       </c>
       <c r="R30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S30" t="s">
         <v>49</v>
@@ -4146,7 +4143,7 @@
         <v>34</v>
       </c>
       <c r="U30" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="V30" t="s">
         <v>36</v>
@@ -4155,10 +4152,10 @@
         <v>3644354666</v>
       </c>
       <c r="X30" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y30" t="s">
         <v>273</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>274</v>
       </c>
       <c r="Z30" t="s">
         <v>36</v>
@@ -4167,7 +4164,7 @@
         <v>1130212806</v>
       </c>
       <c r="AB30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.35">
@@ -4175,31 +4172,31 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31" t="s">
         <v>276</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>277</v>
       </c>
-      <c r="D31" t="s">
-        <v>278</v>
-      </c>
       <c r="E31" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F31" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>310</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>311</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I31" t="s">
+        <v>278</v>
+      </c>
+      <c r="J31" t="s">
         <v>279</v>
-      </c>
-      <c r="J31" t="s">
-        <v>280</v>
       </c>
       <c r="K31" s="9">
         <v>150</v>
@@ -4253,7 +4250,7 @@
         <v>3715616068</v>
       </c>
       <c r="AB31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.35">
@@ -4261,31 +4258,31 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C32" t="s">
         <v>281</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>282</v>
       </c>
-      <c r="D32" t="s">
-        <v>283</v>
-      </c>
       <c r="E32" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>319</v>
-      </c>
       <c r="G32" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>231</v>
       </c>
       <c r="I32" t="s">
+        <v>283</v>
+      </c>
+      <c r="J32" t="s">
         <v>284</v>
-      </c>
-      <c r="J32" t="s">
-        <v>285</v>
       </c>
       <c r="K32" s="10">
         <v>300</v>
@@ -4315,7 +4312,7 @@
         <v>48</v>
       </c>
       <c r="T32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="U32" t="s">
         <v>243</v>
@@ -4330,7 +4327,7 @@
         <v>244</v>
       </c>
       <c r="Y32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Z32" t="s">
         <v>36</v>
@@ -4339,7 +4336,7 @@
         <v>3483408310</v>
       </c>
       <c r="AB32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.35">
@@ -4347,31 +4344,31 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" t="s">
         <v>289</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>290</v>
       </c>
-      <c r="D33" t="s">
-        <v>291</v>
-      </c>
       <c r="E33" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>321</v>
-      </c>
       <c r="G33" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>231</v>
       </c>
       <c r="I33" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K33" s="9">
         <v>44</v>
@@ -4404,7 +4401,7 @@
         <v>34</v>
       </c>
       <c r="U33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="V33" t="s">
         <v>36</v>
@@ -4413,7 +4410,7 @@
         <v>3482322533</v>
       </c>
       <c r="X33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y33" t="s">
         <v>245</v>
@@ -4433,31 +4430,31 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>294</v>
+      </c>
+      <c r="C34" t="s">
         <v>295</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>296</v>
       </c>
-      <c r="D34" t="s">
-        <v>297</v>
-      </c>
       <c r="E34" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>231</v>
       </c>
       <c r="I34" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K34" s="10">
         <v>85</v>
@@ -4487,7 +4484,7 @@
         <v>34</v>
       </c>
       <c r="U34" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="V34" t="s">
         <v>36</v>
@@ -4496,19 +4493,19 @@
         <v>3794246610</v>
       </c>
       <c r="X34" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y34" t="s">
         <v>300</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="Z34" t="s">
         <v>301</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>302</v>
       </c>
       <c r="AA34">
         <v>3458456470</v>
       </c>
       <c r="AB34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
